--- a/data/trans_camb/P05B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P05B_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-1,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,14</t>
+          <t>-3,16; 0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,15</t>
+          <t>-3,45; -0,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -0,47</t>
+          <t>-3,77; -0,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,71</t>
+          <t>-3,06; 0,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,44</t>
+          <t>-2,39; 2,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,89</t>
+          <t>-3,56; 0,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,22</t>
+          <t>-2,86; -0,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,56</t>
+          <t>-2,43; 0,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,29</t>
+          <t>-3,23; -0,45</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-82,34%</t>
+          <t>-84,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-38,05%</t>
+          <t>-48,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-61,32%</t>
+          <t>-65,75%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 30,52</t>
+          <t>-88,59; 28,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-93,39; 17,63</t>
+          <t>-100,0; 28,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,61</t>
+          <t>-100,0; 4,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-75,85; 59,57</t>
+          <t>-78,13; 57,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,43; 125,58</t>
+          <t>-64,53; 120,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,55; 107,59</t>
+          <t>-89,21; 63,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,63; -2,54</t>
+          <t>-76,72; -1,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 32,43</t>
+          <t>-71,9; 21,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,4; -4,92</t>
+          <t>-88,74; -8,51</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,24</t>
+          <t>-3,03; 0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,03</t>
+          <t>-3,29; -0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,63</t>
+          <t>-2,96; 1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,82</t>
+          <t>-4,94; -0,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,39</t>
+          <t>-4,89; -0,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -1,37</t>
+          <t>-5,52; -1,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,88</t>
+          <t>-3,42; -0,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,84</t>
+          <t>-3,57; -0,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,6</t>
+          <t>-3,59; -0,79</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,99%</t>
+          <t>-36,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-72,18%</t>
+          <t>-72,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-54,47%</t>
+          <t>-57,33%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,62; 14,13</t>
+          <t>-72,62; 32,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 9,77</t>
+          <t>-81,82; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 83,41</t>
+          <t>-78,84; 58,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,16; -25,72</t>
+          <t>-81,16; -16,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,12; -8,22</t>
+          <t>-79,77; -9,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,07; -28,74</t>
+          <t>-90,77; -29,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,33; -25,18</t>
+          <t>-71,77; -21,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,17; -23,88</t>
+          <t>-75,85; -29,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,68; -12,88</t>
+          <t>-79,21; -19,97</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-3,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,27</t>
+          <t>-3,6; 0,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,86</t>
+          <t>-4,58; -0,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,84</t>
+          <t>-4,43; -0,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -1,6</t>
+          <t>-6,14; -1,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -1,92</t>
+          <t>-6,26; -1,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -3,4</t>
+          <t>-7,19; -3,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,38</t>
+          <t>-4,19; -1,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -1,91</t>
+          <t>-4,63; -1,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -2,67</t>
+          <t>-5,33; -2,62</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-70,19%</t>
+          <t>-73,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-86,47%</t>
+          <t>-86,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-80,62%</t>
+          <t>-81,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 17,1</t>
+          <t>-73,53; 18,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,45; -20,69</t>
+          <t>-88,45; -25,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,7; -6,3</t>
+          <t>-91,45; -22,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,07; -35,32</t>
+          <t>-82,85; -38,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,1; -38,12</t>
+          <t>-83,09; -39,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-94,89; -67,7</t>
+          <t>-95,47; -68,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,19; -32,63</t>
+          <t>-74,7; -33,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,2; -48,9</t>
+          <t>-82,29; -49,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,18; -62,51</t>
+          <t>-91,48; -64,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-2,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,26</t>
+          <t>-1,54; 2,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,44</t>
+          <t>-2,1; 1,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; -0,31</t>
+          <t>-3,08; -0,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; -0,81</t>
+          <t>-5,02; -0,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,21</t>
+          <t>-4,22; -0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -1,44</t>
+          <t>-4,89; -1,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,16</t>
+          <t>-2,51; 0,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,18</t>
+          <t>-2,65; 0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -1,26</t>
+          <t>-3,39; -1,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-76,48%</t>
+          <t>-69,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-73,69%</t>
+          <t>-72,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-75,68%</t>
+          <t>-71,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,48; 218,4</t>
+          <t>-59,22; 224,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 137,24</t>
+          <t>-71,34; 172,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-95,88; -8,16</t>
+          <t>-92,97; 28,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-88,85; -20,38</t>
+          <t>-88,55; -24,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,77; -0,2</t>
+          <t>-80,46; -5,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,68; -46,22</t>
+          <t>-86,6; -40,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 11,38</t>
+          <t>-65,59; 8,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 11,38</t>
+          <t>-68,05; 6,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,64; -53,57</t>
+          <t>-85,26; -46,06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-2,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,59</t>
+          <t>-4,91; -0,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,57</t>
+          <t>-4,99; -0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,33</t>
+          <t>-5,1; -0,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -1,1</t>
+          <t>-6,01; -1,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -1,17</t>
+          <t>-6,18; -1,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -1,25</t>
+          <t>-5,87; -1,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -1,37</t>
+          <t>-4,83; -1,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; -1,45</t>
+          <t>-4,74; -1,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,28</t>
+          <t>-4,63; -1,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-61,01%</t>
+          <t>-64,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-67,13%</t>
+          <t>-66,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-64,52%</t>
+          <t>-65,72%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-92,6; -10,99</t>
+          <t>-90,71; -10,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-90,38; -12,05</t>
+          <t>-91,47; -5,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,99; -7,76</t>
+          <t>-86,37; -15,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-91,41; -29,84</t>
+          <t>-90,57; -33,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-89,43; -28,58</t>
+          <t>-90,82; -28,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,32; -33,69</t>
+          <t>-83,6; -31,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-85,45; -38,12</t>
+          <t>-86,77; -42,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-84,97; -41,34</t>
+          <t>-85,85; -35,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-78,14; -37,51</t>
+          <t>-80,52; -41,46</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,82</t>
+          <t>-4,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-2,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,86</t>
+          <t>-2,05; 0,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,0</t>
+          <t>-1,32; 2,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,79</t>
+          <t>-1,41; 1,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -2,94</t>
+          <t>-8,38; -3,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -1,06</t>
+          <t>-6,71; -1,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -2,74</t>
+          <t>-7,34; -2,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; -1,73</t>
+          <t>-4,81; -1,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,39</t>
+          <t>-3,74; -0,21</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -1,08</t>
+          <t>-3,86; -0,91</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-81,28%</t>
+          <t>-73,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-67,28%</t>
+          <t>-58,83%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 533,99</t>
+          <t>-82,05; 690,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,21; 500,81</t>
+          <t>-67,02; 525,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -46,08</t>
+          <t>-100,0; -43,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-84,95; -19,14</t>
+          <t>-84,64; -20,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-94,75; -60,42</t>
+          <t>-86,8; -46,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-96,9; -52,31</t>
+          <t>-96,26; -40,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -11,49</t>
+          <t>-77,96; -2,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-86,71; -38,84</t>
+          <t>-78,14; -30,18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-3,73</t>
+          <t>-3,79</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,84</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-3,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,21</t>
+          <t>-6,17; -0,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,45</t>
+          <t>-5,74; 0,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -1,54</t>
+          <t>-7,15; -1,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,89</t>
+          <t>-5,02; 0,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,12</t>
+          <t>-3,87; 2,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -0,76</t>
+          <t>-5,61; -0,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,46; -0,38</t>
+          <t>-4,53; -0,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,6</t>
+          <t>-3,75; 0,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -1,6</t>
+          <t>-5,3; -1,56</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-81,64%</t>
+          <t>-82,84%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-69,71%</t>
+          <t>-70,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-74,76%</t>
+          <t>-75,66%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-93,1; 6,26</t>
+          <t>-91,88; 18,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,58; 27,85</t>
+          <t>-84,48; 37,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-96,04; -45,9</t>
+          <t>-95,76; -39,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-78,81; 38,92</t>
+          <t>-81,05; 38,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-70,79; 97,29</t>
+          <t>-72,34; 101,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-87,87; -21,83</t>
+          <t>-87,64; -23,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-79,1; -9,55</t>
+          <t>-78,95; -7,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 20,4</t>
+          <t>-68,01; 29,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-87,49; -51,44</t>
+          <t>-87,72; -52,32</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,46</t>
+          <t>-3,41</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,03; -0,53</t>
+          <t>-2,04; -0,57</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,8</t>
+          <t>-2,32; -0,91</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -1,13</t>
+          <t>-2,57; -1,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,95; -2,26</t>
+          <t>-3,92; -2,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -1,68</t>
+          <t>-3,54; -1,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -2,68</t>
+          <t>-4,22; -2,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -1,59</t>
+          <t>-2,76; -1,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -1,53</t>
+          <t>-2,71; -1,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -2,12</t>
+          <t>-3,17; -2,13</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-63,46%</t>
+          <t>-63,51%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-73,84%</t>
+          <t>-72,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-69,87%</t>
+          <t>-69,22%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-60,6; -20,57</t>
+          <t>-60,55; -22,58</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,37; -31,68</t>
+          <t>-68,54; -33,87</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -43,0</t>
+          <t>-75,21; -45,68</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -53,51</t>
+          <t>-74,84; -51,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-65,78; -39,58</t>
+          <t>-66,53; -40,91</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -64,06</t>
+          <t>-80,34; -63,61</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-65,27; -46,11</t>
+          <t>-65,84; -46,23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,75; -43,66</t>
+          <t>-64,08; -43,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-76,91; -61,6</t>
+          <t>-76,13; -61,83</t>
         </is>
       </c>
     </row>
